--- a/accountant_excel_test_template.xlsx
+++ b/accountant_excel_test_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel Test" sheetId="1" r:id="Rad56d7cc5d63419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel Test" sheetId="1" r:id="R37d23ab05c98422a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +39,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -71,11 +71,6 @@
         <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD9EAF7"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -84,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -165,9 +160,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -385,8 +377,8 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="45" t="str">
-        <x:v>TIME: 10 MINUTES  |  TOTAL: 10 MARKS  |  1 MARK PER TASK</x:v>
+      <x:c r="A2" s="12" t="str">
+        <x:v>TIME: 5 MINUTES  |  TOTAL: 10 MARKS  |  1 MARK PER TASK</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -395,17 +387,13 @@
       </x:c>
       <x:c r="B4" t="str"/>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
+    <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="16" t="str">
-        <x:v>Instructions</x:v>
+        <x:v>Test Note</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>Open this workbook in Microsoft Excel. Complete the yellow answer cells in E22:E31. You may enter either a calculated result or an Excel formula. Save the completed workbook as .xlsx and upload it back to the test page before the 10-minute limit.</x:v>
-      </x:c>
-      <x:c r="C5" s="18"/>
-      <x:c r="D5" s="18"/>
-      <x:c r="E5" s="18"/>
-      <x:c r="F5" s="18"/>
+        <x:v>Open this workbook in Microsoft Excel. Complete the yellow answer cells. Save the completed workbook, then upload it back to the test page before time expires.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
